--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -537,19 +537,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e_w658600169-400_POL</t>
+          <t>e_Warsaw_POL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
+          <t>grid node -- way/29115701-220 (Warsaw, 9 km)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>766</v>
+        <v>808</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e_w183945016-220_POL</t>
+          <t>e_Sosnowiec_POL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -593,19 +593,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_w180535363-220_POL</t>
+          <t>e_Poznan_POL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
+          <t>grid node -- way/32036484-220 (Poznan, 11 km)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -624,19 +624,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e_w121656686-220_POL</t>
+          <t>e_Krakow_POL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
+          <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -655,79 +655,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e_w87667718-220_POL</t>
+          <t>e_Wroclaw_POL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
+          <t>grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_PL34-400_POL</t>
+          <t>e_Gdansk_POL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
+          <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_w112614319-400_POL</t>
+          <t>e_Lomza_POL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+          <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_PL15-400_POL</t>
+          <t>e_Katowice_POL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
+          <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_w40946790-220_POL</t>
+          <t>e_Gliwice_POL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
+          <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -743,12 +743,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_w293489607-400_POL</t>
+          <t>e_PiotrkowTrybunalsk_POL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
+          <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -807,16 +807,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_w170316833-220_POL</t>
+          <t>e_Bialystok_POL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+          <t>grid node -- PL17-400 (Bialystok, 26 km)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -850,16 +850,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e_w303870256-400_POL</t>
+          <t>e_Bydgoszcz_POL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
+          <t>grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_w101915790-220_POL</t>
+          <t>e_Olsztyn_POL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e_w245964556-220_POL</t>
+          <t>e_Wloclawek_POL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -976,7 +976,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e_w88544449-220_POL</t>
+          <t>e_Pulawy_POL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>e_w165763717-220_POL</t>
+          <t>e_Police_POL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>e_w171917072-400_POL</t>
+          <t>e_Radomsko_POL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1052,7 +1052,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>e_w198635989-220_POL</t>
+          <t>e_Debica_POL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>e_w255277953-400_POL</t>
+          <t>e_Opole_POL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1085,6 +1085,19 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>e_Konin_POL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>process</t>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DC details" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DC details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC details" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
